--- a/artfynd/A 30098-2021 artfynd.xlsx
+++ b/artfynd/A 30098-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133465907</v>
       </c>
       <c r="B2" t="n">
-        <v>80438</v>
+        <v>80439</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 30098-2021 artfynd.xlsx
+++ b/artfynd/A 30098-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133465907</v>
       </c>
       <c r="B2" t="n">
-        <v>80439</v>
+        <v>80453</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 30098-2021 artfynd.xlsx
+++ b/artfynd/A 30098-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133465907</v>
       </c>
       <c r="B2" t="n">
-        <v>80453</v>
+        <v>80473</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 30098-2021 artfynd.xlsx
+++ b/artfynd/A 30098-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133465907</v>
       </c>
       <c r="B2" t="n">
-        <v>80473</v>
+        <v>80474</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
